--- a/data/raw/walmart_format_test.xlsx
+++ b/data/raw/walmart_format_test.xlsx
@@ -431,17 +431,17 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>product_raw</t>
+          <t>producto_original</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>price_mxn</t>
+          <t>precio_mxn</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>product_canonical</t>
+          <t>producto_canonico</t>
         </is>
       </c>
     </row>
